--- a/terabytee.xlsx
+++ b/terabytee.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\terab\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\xxx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{005B60DF-7D63-4F8B-B594-C7E017985F58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BBE8EAA-8DC2-4EB0-9D6A-1A215C353AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{95AEDD9A-F9D3-4C7B-9550-CDC18FDA07A0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="1">
   <si>
     <t>FERO JELEK</t>
   </si>
@@ -379,11 +379,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39B26B72-D1A6-42C5-B499-BFF791C78475}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.77734375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
